--- a/planningPhase/develop_plan.xlsx
+++ b/planningPhase/develop_plan.xlsx
@@ -1949,469 +1949,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>받는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사람에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>상세한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>편지를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>통해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>선물하는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사람과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>받는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사람간의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관계</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>증진</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.
-2. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>선물을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>하는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>것보다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>상대를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>명확히</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>아는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>것이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>더</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>중요하다는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사용자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>경험</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>제공</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>1</t>
     </r>
     <r>
@@ -13102,6 +12639,698 @@
         <charset val="129"/>
       </rPr>
       <t>감소시킴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>받는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사람에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상세한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>편지를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>통해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>선물하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사람과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>받는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사람간의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>선물을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것보다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상대를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명확히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>중요하다는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>경험</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>글로벌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>판매</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가능한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한국</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제품을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>투입하여</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스코빌이라는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명칭에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>걸맞은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>행보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보이기</t>
     </r>
     <r>
       <rPr>
@@ -13381,6 +13610,42 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -13408,44 +13673,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13904,116 +14133,116 @@
   <sheetData>
     <row r="1" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="3" t="s">
-        <v>30</v>
+      <c r="B2" s="15" t="s">
+        <v>29</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="18">
         <v>45857</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="20"/>
     </row>
     <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>13</v>
+      <c r="C4" s="21" t="s">
+        <v>12</v>
       </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="11"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="23"/>
     </row>
     <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>16</v>
+      <c r="C5" s="24" t="s">
+        <v>15</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="14"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="17" t="s">
-        <v>29</v>
+      <c r="B6" s="3" t="s">
+        <v>28</v>
       </c>
-      <c r="C6" s="22" t="s">
-        <v>31</v>
+      <c r="C6" s="12" t="s">
+        <v>30</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="24"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="14"/>
     </row>
     <row r="7" spans="2:6" ht="82.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>18</v>
+      <c r="C7" s="6" t="s">
+        <v>17</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="14"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" spans="2:6" ht="91.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>19</v>
+      <c r="C8" s="6" t="s">
+        <v>18</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="14"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>12</v>
+      <c r="C9" s="6" t="s">
+        <v>42</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="14"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8"/>
     </row>
     <row r="10" spans="2:6" ht="123" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>20</v>
+      <c r="C10" s="6" t="s">
+        <v>19</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="14"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" spans="2:6" ht="63.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="16"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="11"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B13" s="20" t="s">
-        <v>23</v>
+      <c r="B13" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -14047,114 +14276,114 @@
   <sheetData>
     <row r="1" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="3" t="s">
-        <v>33</v>
+      <c r="B2" s="15" t="s">
+        <v>32</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="18">
         <v>45857</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="20"/>
     </row>
     <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="11"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="23"/>
     </row>
     <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>16</v>
+      <c r="C5" s="24" t="s">
+        <v>15</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="14"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="17" t="s">
-        <v>29</v>
+      <c r="B6" s="3" t="s">
+        <v>28</v>
       </c>
-      <c r="C6" s="22" t="s">
-        <v>32</v>
+      <c r="C6" s="12" t="s">
+        <v>31</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="24"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="14"/>
     </row>
     <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="14"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>14</v>
+      <c r="C8" s="6" t="s">
+        <v>13</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="14"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="14"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8"/>
     </row>
     <row r="10" spans="2:6" ht="130.80000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>15</v>
+      <c r="C10" s="6" t="s">
+        <v>14</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="14"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" spans="2:6" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="16"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="11"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B13" s="20" t="s">
-        <v>24</v>
+      <c r="B13" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -14188,114 +14417,114 @@
   <sheetData>
     <row r="1" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="3" t="s">
-        <v>36</v>
+      <c r="B2" s="15" t="s">
+        <v>35</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="18">
         <v>45857</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="20"/>
     </row>
     <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="11"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="23"/>
     </row>
     <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>17</v>
+      <c r="C5" s="24" t="s">
+        <v>16</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="14"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="17" t="s">
-        <v>29</v>
+      <c r="B6" s="3" t="s">
+        <v>28</v>
       </c>
-      <c r="C6" s="22" t="s">
-        <v>35</v>
+      <c r="C6" s="12" t="s">
+        <v>34</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="24"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="14"/>
     </row>
     <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>28</v>
+      <c r="C7" s="6" t="s">
+        <v>27</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="14"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>26</v>
+      <c r="C8" s="6" t="s">
+        <v>25</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="14"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>21</v>
+      <c r="C9" s="6" t="s">
+        <v>20</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="14"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8"/>
     </row>
     <row r="10" spans="2:6" ht="130.80000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>27</v>
+      <c r="C10" s="6" t="s">
+        <v>26</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="14"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" spans="2:6" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="19" t="s">
-        <v>25</v>
+      <c r="C11" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="16"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="11"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B13" s="21" t="s">
-        <v>22</v>
+      <c r="B13" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -14329,113 +14558,113 @@
   <sheetData>
     <row r="1" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="3" t="s">
-        <v>37</v>
+      <c r="B2" s="15" t="s">
+        <v>36</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="18">
         <v>45857</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="20"/>
     </row>
     <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="11"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="23"/>
     </row>
     <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>17</v>
+      <c r="C5" s="24" t="s">
+        <v>16</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="14"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="17" t="s">
-        <v>29</v>
+      <c r="B6" s="3" t="s">
+        <v>28</v>
       </c>
-      <c r="C6" s="22" t="s">
-        <v>34</v>
+      <c r="C6" s="12" t="s">
+        <v>33</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="24"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="14"/>
     </row>
     <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>40</v>
+      <c r="C7" s="6" t="s">
+        <v>39</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="14"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>42</v>
+      <c r="C8" s="6" t="s">
+        <v>41</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="14"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>41</v>
+      <c r="C9" s="6" t="s">
+        <v>40</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="14"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8"/>
     </row>
     <row r="10" spans="2:6" ht="130.80000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>39</v>
+      <c r="C10" s="6" t="s">
+        <v>38</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="14"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" spans="2:6" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="19" t="s">
-        <v>38</v>
+      <c r="C11" s="9" t="s">
+        <v>37</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="16"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="11"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B13" s="21"/>
+      <c r="B13" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/planningPhase/develop_plan.xlsx
+++ b/planningPhase/develop_plan.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TJ-BU-702-24PC\Desktop\cording\kafella92.github.io\planningPhase\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB4C63B-C8B9-4CF6-A3DE-A1E832A94D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="192" yWindow="108" windowWidth="16776" windowHeight="5592"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="heartpigeon(solo)" sheetId="4" r:id="rId1"/>
@@ -13347,7 +13353,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -13686,6 +13692,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -13707,7 +13716,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -13756,7 +13771,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -13805,7 +13826,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2"/>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -13880,7 +13907,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -13913,9 +13940,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -13948,6 +13992,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -14123,16 +14184,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:F13"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.8984375" customWidth="1"/>
+    <col min="1" max="1" width="1.875" customWidth="1"/>
     <col min="4" max="4" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="15" t="s">
         <v>29</v>
       </c>
@@ -14141,7 +14202,7 @@
       <c r="E2" s="16"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -14152,7 +14213,7 @@
       <c r="E3" s="19"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -14163,7 +14224,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="23"/>
     </row>
-    <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -14174,7 +14235,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
@@ -14185,7 +14246,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="2:6" ht="82.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" ht="82.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -14196,7 +14257,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="2:6" ht="91.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" ht="91.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
@@ -14207,7 +14268,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -14218,7 +14279,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="2:6" ht="123" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="123" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
@@ -14229,7 +14290,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="2:6" ht="63.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="63.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -14240,7 +14301,7 @@
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>22</v>
       </c>
@@ -14266,16 +14327,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:F13"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.3984375" customWidth="1"/>
+    <col min="1" max="1" width="2.375" customWidth="1"/>
     <col min="4" max="4" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="15" t="s">
         <v>32</v>
       </c>
@@ -14284,7 +14345,7 @@
       <c r="E2" s="16"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -14295,7 +14356,7 @@
       <c r="E3" s="19"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -14304,7 +14365,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="23"/>
     </row>
-    <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -14315,7 +14376,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
@@ -14326,7 +14387,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -14337,7 +14398,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
@@ -14348,7 +14409,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -14359,7 +14420,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="2:6" ht="130.80000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="130.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
@@ -14370,7 +14431,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="2:6" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -14381,7 +14442,7 @@
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>23</v>
       </c>
@@ -14407,16 +14468,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:F13"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.3984375" customWidth="1"/>
+    <col min="1" max="1" width="2.375" customWidth="1"/>
     <col min="4" max="4" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="15" t="s">
         <v>35</v>
       </c>
@@ -14425,7 +14486,7 @@
       <c r="E2" s="16"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -14436,7 +14497,7 @@
       <c r="E3" s="19"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -14445,7 +14506,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="23"/>
     </row>
-    <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -14456,7 +14517,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
@@ -14467,7 +14528,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -14478,7 +14539,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
@@ -14489,7 +14550,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -14500,7 +14561,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="2:6" ht="130.80000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="130.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
@@ -14511,7 +14572,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="2:6" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -14522,7 +14583,7 @@
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="5" t="s">
         <v>21</v>
       </c>
@@ -14548,16 +14609,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:F13"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.3984375" customWidth="1"/>
+    <col min="1" max="1" width="2.375" customWidth="1"/>
     <col min="4" max="4" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="15" t="s">
         <v>36</v>
       </c>
@@ -14566,7 +14627,7 @@
       <c r="E2" s="16"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -14577,7 +14638,7 @@
       <c r="E3" s="19"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -14586,7 +14647,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="23"/>
     </row>
-    <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -14597,7 +14658,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
@@ -14608,7 +14669,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -14619,7 +14680,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
@@ -14630,7 +14691,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -14641,7 +14702,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="2:6" ht="130.80000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="130.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
@@ -14652,7 +14713,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="2:6" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -14663,7 +14724,7 @@
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="5"/>
     </row>
   </sheetData>

--- a/planningPhase/develop_plan.xlsx
+++ b/planningPhase/develop_plan.xlsx
@@ -1,29 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TJ-BU-702-24PC\Desktop\cording\kafella92.github.io\planningPhase\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB4C63B-C8B9-4CF6-A3DE-A1E832A94D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23256" windowHeight="13176" firstSheet="4" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="heartpigeon(solo)" sheetId="4" r:id="rId1"/>
     <sheet name="saykorean(solo)" sheetId="1" r:id="rId2"/>
     <sheet name="dageMark(team)" sheetId="5" r:id="rId3"/>
     <sheet name="standByFiveMinutesAgo(team)" sheetId="6" r:id="rId4"/>
+    <sheet name="HappyandNavi(solo)" sheetId="8" r:id="rId5"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="48">
   <si>
     <t>기간</t>
   </si>
@@ -13349,11 +13344,377 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프로젝트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기획서</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> : </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반려동물</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일상</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기록</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추억</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공유</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어플</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> &gt;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해피야나비야(Happy and Navi)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>출산율</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저하에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반비례하여</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반려동물</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>키우는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사람은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>늘어나고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">있음
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고양이, 강아지 등 반려동물 키우는 사람</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -13719,7 +14080,7 @@
         <xdr:cNvPr id="2" name="그림 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13774,7 +14135,7 @@
         <xdr:cNvPr id="2" name="그림 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13829,7 +14190,7 @@
         <xdr:cNvPr id="3" name="그림 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13907,7 +14268,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -13940,26 +14301,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -13992,23 +14336,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -14184,16 +14511,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:F13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="1.875" customWidth="1"/>
+    <col min="1" max="1" width="1.8984375" customWidth="1"/>
     <col min="4" max="4" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="15" t="s">
         <v>29</v>
       </c>
@@ -14202,7 +14529,7 @@
       <c r="E2" s="16"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="2:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -14213,7 +14540,7 @@
       <c r="E3" s="19"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -14224,7 +14551,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="23"/>
     </row>
-    <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -14235,7 +14562,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
@@ -14246,7 +14573,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="2:6" ht="82.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" ht="82.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -14257,7 +14584,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="2:6" ht="91.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:6" ht="91.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
@@ -14268,7 +14595,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -14279,7 +14606,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="2:6" ht="123" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" ht="123" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
@@ -14290,7 +14617,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="2:6" ht="63.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" ht="63.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -14301,7 +14628,7 @@
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="4" t="s">
         <v>22</v>
       </c>
@@ -14327,16 +14654,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:F13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.375" customWidth="1"/>
+    <col min="1" max="1" width="2.3984375" customWidth="1"/>
     <col min="4" max="4" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="15" t="s">
         <v>32</v>
       </c>
@@ -14345,7 +14672,7 @@
       <c r="E2" s="16"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="2:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -14356,7 +14683,7 @@
       <c r="E3" s="19"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -14365,7 +14692,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="23"/>
     </row>
-    <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -14376,7 +14703,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
@@ -14387,7 +14714,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -14398,7 +14725,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
@@ -14409,7 +14736,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -14420,7 +14747,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="2:6" ht="130.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" ht="130.94999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
@@ -14431,7 +14758,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="2:6" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -14442,7 +14769,7 @@
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="4" t="s">
         <v>23</v>
       </c>
@@ -14468,16 +14795,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:F13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.375" customWidth="1"/>
+    <col min="1" max="1" width="2.3984375" customWidth="1"/>
     <col min="4" max="4" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="15" t="s">
         <v>35</v>
       </c>
@@ -14486,7 +14813,7 @@
       <c r="E2" s="16"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="2:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -14497,7 +14824,7 @@
       <c r="E3" s="19"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -14506,7 +14833,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="23"/>
     </row>
-    <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -14517,7 +14844,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
@@ -14528,7 +14855,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -14539,7 +14866,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
@@ -14550,7 +14877,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -14561,7 +14888,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="2:6" ht="130.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" ht="130.94999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
@@ -14572,7 +14899,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="2:6" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -14583,7 +14910,7 @@
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="5" t="s">
         <v>21</v>
       </c>
@@ -14609,16 +14936,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:F13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.375" customWidth="1"/>
+    <col min="1" max="1" width="2.3984375" customWidth="1"/>
     <col min="4" max="4" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="15" t="s">
         <v>36</v>
       </c>
@@ -14627,7 +14954,7 @@
       <c r="E2" s="16"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="2:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -14638,7 +14965,7 @@
       <c r="E3" s="19"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -14647,7 +14974,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="23"/>
     </row>
-    <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -14658,7 +14985,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
@@ -14669,7 +14996,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -14680,7 +15007,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
@@ -14691,7 +15018,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -14702,7 +15029,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="2:6" ht="130.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" ht="130.94999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
@@ -14713,7 +15040,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="2:6" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -14724,7 +15051,7 @@
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B13" s="5"/>
     </row>
   </sheetData>
@@ -14744,4 +15071,136 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:F13"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="2.3984375" customWidth="1"/>
+    <col min="4" max="4" width="40.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="17"/>
+    </row>
+    <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="18">
+        <v>45872</v>
+      </c>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="20"/>
+    </row>
+    <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="21"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="23"/>
+    </row>
+    <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
+    </row>
+    <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="14"/>
+    </row>
+    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" spans="2:6" ht="130.94999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" spans="2:6" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="11"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B13" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/planningPhase/develop_plan.xlsx
+++ b/planningPhase/develop_plan.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tj-bu-702-07\Desktop\cording\kafella92.github.io\planningPhase\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB9879D-2F5E-4071-91C9-BA15D079AAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23256" windowHeight="13176" firstSheet="4" activeTab="4"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="heartpigeon(solo)" sheetId="4" r:id="rId1"/>
@@ -14,6 +20,11 @@
     <sheet name="HappyandNavi(solo)" sheetId="8" r:id="rId5"/>
   </sheets>
   <calcPr calcId="144525"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -13714,7 +13725,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -14080,7 +14091,7 @@
         <xdr:cNvPr id="2" name="그림 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14135,7 +14146,7 @@
         <xdr:cNvPr id="2" name="그림 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14190,7 +14201,7 @@
         <xdr:cNvPr id="3" name="그림 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14268,7 +14279,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -14301,9 +14312,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -14336,6 +14364,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -14511,16 +14556,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:F13"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.8984375" customWidth="1"/>
+    <col min="1" max="1" width="1.875" customWidth="1"/>
     <col min="4" max="4" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="15" t="s">
         <v>29</v>
       </c>
@@ -14529,7 +14574,7 @@
       <c r="E2" s="16"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -14540,7 +14585,7 @@
       <c r="E3" s="19"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -14551,7 +14596,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="23"/>
     </row>
-    <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -14562,7 +14607,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
@@ -14573,7 +14618,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="2:6" ht="82.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" ht="82.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -14584,7 +14629,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="2:6" ht="91.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" ht="91.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
@@ -14595,7 +14640,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -14606,7 +14651,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="2:6" ht="123" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="123" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
@@ -14617,7 +14662,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="2:6" ht="63.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="63.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -14628,7 +14673,7 @@
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>22</v>
       </c>
@@ -14654,16 +14699,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:F13"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.3984375" customWidth="1"/>
+    <col min="1" max="1" width="2.375" customWidth="1"/>
     <col min="4" max="4" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="15" t="s">
         <v>32</v>
       </c>
@@ -14672,7 +14717,7 @@
       <c r="E2" s="16"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -14683,7 +14728,7 @@
       <c r="E3" s="19"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -14692,7 +14737,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="23"/>
     </row>
-    <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -14703,7 +14748,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
@@ -14714,7 +14759,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -14725,7 +14770,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
@@ -14736,7 +14781,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -14747,7 +14792,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="2:6" ht="130.94999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="130.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
@@ -14758,7 +14803,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="2:6" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -14769,7 +14814,7 @@
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>23</v>
       </c>
@@ -14795,16 +14840,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:F13"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.3984375" customWidth="1"/>
+    <col min="1" max="1" width="2.375" customWidth="1"/>
     <col min="4" max="4" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="15" t="s">
         <v>35</v>
       </c>
@@ -14813,7 +14858,7 @@
       <c r="E2" s="16"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -14824,7 +14869,7 @@
       <c r="E3" s="19"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -14833,7 +14878,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="23"/>
     </row>
-    <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -14844,7 +14889,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
@@ -14855,7 +14900,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -14866,7 +14911,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
@@ -14877,7 +14922,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -14888,7 +14933,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="2:6" ht="130.94999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="130.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
@@ -14899,7 +14944,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="2:6" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -14910,7 +14955,7 @@
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="5" t="s">
         <v>21</v>
       </c>
@@ -14936,16 +14981,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:F13"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.3984375" customWidth="1"/>
+    <col min="1" max="1" width="2.375" customWidth="1"/>
     <col min="4" max="4" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="15" t="s">
         <v>36</v>
       </c>
@@ -14954,7 +14999,7 @@
       <c r="E2" s="16"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -14965,7 +15010,7 @@
       <c r="E3" s="19"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -14974,7 +15019,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="23"/>
     </row>
-    <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -14985,7 +15030,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
@@ -14996,7 +15041,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -15007,7 +15052,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
@@ -15018,7 +15063,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -15029,7 +15074,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="2:6" ht="130.94999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="130.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
@@ -15040,7 +15085,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="2:6" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -15051,7 +15096,7 @@
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
     </row>
-    <row r="13" spans="2:6" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="5"/>
     </row>
   </sheetData>
@@ -15074,16 +15119,16 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:F13"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.3984375" customWidth="1"/>
+    <col min="1" max="1" width="2.375" customWidth="1"/>
     <col min="4" max="4" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="15" t="s">
         <v>43</v>
       </c>
@@ -15092,7 +15137,7 @@
       <c r="E2" s="16"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -15103,7 +15148,7 @@
       <c r="E3" s="19"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -15112,7 +15157,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="23"/>
     </row>
-    <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -15123,7 +15168,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
@@ -15134,7 +15179,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -15145,7 +15190,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
@@ -15154,7 +15199,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -15163,7 +15208,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="2:6" ht="130.94999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="130.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
@@ -15172,7 +15217,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="2:6" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -15183,7 +15228,7 @@
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="5"/>
     </row>
   </sheetData>

--- a/planningPhase/develop_plan.xlsx
+++ b/planningPhase/develop_plan.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tj-bu-702-07\Desktop\cording\kafella92.github.io\planningPhase\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB9879D-2F5E-4071-91C9-BA15D079AAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23256" windowHeight="13176" firstSheet="4" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="heartpigeon(solo)" sheetId="4" r:id="rId1"/>
@@ -9196,10 +9190,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>공연5분전(Stand by five minutes ago)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>따거마크(Dage Mark)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -13721,11 +13711,15 @@
     <t>고양이, 강아지 등 반려동물 키우는 사람</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>공연5분전(Stand by five minutes ago)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -14091,7 +14085,7 @@
         <xdr:cNvPr id="2" name="그림 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14146,7 +14140,7 @@
         <xdr:cNvPr id="2" name="그림 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14201,7 +14195,7 @@
         <xdr:cNvPr id="3" name="그림 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14279,7 +14273,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -14312,26 +14306,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -14364,23 +14341,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -14556,16 +14516,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:F13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="1.875" customWidth="1"/>
+    <col min="1" max="1" width="1.8984375" customWidth="1"/>
     <col min="4" max="4" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="15" t="s">
         <v>29</v>
       </c>
@@ -14574,7 +14534,7 @@
       <c r="E2" s="16"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="2:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -14585,7 +14545,7 @@
       <c r="E3" s="19"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -14596,7 +14556,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="23"/>
     </row>
-    <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -14607,7 +14567,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
@@ -14618,7 +14578,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="2:6" ht="82.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" ht="82.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -14629,7 +14589,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="2:6" ht="91.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:6" ht="91.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
@@ -14640,18 +14600,18 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="2:6" ht="123" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" ht="123" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
@@ -14662,7 +14622,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="2:6" ht="63.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" ht="63.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -14673,7 +14633,7 @@
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="4" t="s">
         <v>22</v>
       </c>
@@ -14699,16 +14659,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:F13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.375" customWidth="1"/>
+    <col min="1" max="1" width="2.3984375" customWidth="1"/>
     <col min="4" max="4" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="15" t="s">
         <v>32</v>
       </c>
@@ -14717,7 +14677,7 @@
       <c r="E2" s="16"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="2:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -14728,7 +14688,7 @@
       <c r="E3" s="19"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -14737,7 +14697,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="23"/>
     </row>
-    <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -14748,7 +14708,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
@@ -14759,7 +14719,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -14770,7 +14730,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
@@ -14781,7 +14741,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -14792,7 +14752,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="2:6" ht="130.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" ht="130.94999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
@@ -14803,7 +14763,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="2:6" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -14814,7 +14774,7 @@
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="4" t="s">
         <v>23</v>
       </c>
@@ -14840,25 +14800,25 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:F13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.375" customWidth="1"/>
+    <col min="1" max="1" width="2.3984375" customWidth="1"/>
     <col min="4" max="4" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
       <c r="E2" s="16"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="2:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -14869,7 +14829,7 @@
       <c r="E3" s="19"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -14878,7 +14838,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="23"/>
     </row>
-    <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -14889,18 +14849,18 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -14911,7 +14871,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
@@ -14922,7 +14882,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -14933,7 +14893,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="2:6" ht="130.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" ht="130.94999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
@@ -14944,7 +14904,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="2:6" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -14955,7 +14915,7 @@
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="5" t="s">
         <v>21</v>
       </c>
@@ -14981,25 +14941,25 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:F13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.375" customWidth="1"/>
+    <col min="1" max="1" width="2.3984375" customWidth="1"/>
     <col min="4" max="4" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
       <c r="E2" s="16"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="2:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -15010,7 +14970,7 @@
       <c r="E3" s="19"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -15019,7 +14979,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="23"/>
     </row>
-    <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -15030,73 +14990,73 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="2:6" ht="130.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" ht="130.94999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="2:6" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="5"/>
     </row>
   </sheetData>
@@ -15119,25 +15079,25 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:F13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.375" customWidth="1"/>
+    <col min="1" max="1" width="2.3984375" customWidth="1"/>
     <col min="4" max="4" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:6" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
       <c r="E2" s="16"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="2:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -15148,7 +15108,7 @@
       <c r="E3" s="19"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -15157,40 +15117,40 @@
       <c r="E4" s="22"/>
       <c r="F4" s="23"/>
     </row>
-    <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" ht="105.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:6" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
@@ -15199,7 +15159,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:6" ht="75.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -15208,7 +15168,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="2:6" ht="130.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" ht="130.94999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
@@ -15217,18 +15177,18 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="2:6" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="5"/>
     </row>
   </sheetData>
